--- a/薇拉馮德_台詞差分.xlsx
+++ b/薇拉馮德_台詞差分.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ray Ku\Desktop\TIVOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B0B133-240F-47E8-AEC0-4DDB4C5E833E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579CFED7-8CF1-4083-8091-67E38483CB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4950" yWindow="3180" windowWidth="32055" windowHeight="19215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5790" yWindow="2565" windowWidth="32055" windowHeight="19215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="薇拉馮德" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="326">
   <si>
     <t>名字</t>
   </si>
@@ -1011,6 +1011,9 @@
   <si>
     <t>很可笑吧？只是因為頭髮的顏色隨了母親，就被當成了污點藏在修道院裡。但是…...</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>renna_si_sniveleyes</t>
   </si>
 </sst>
 </file>
@@ -10954,7 +10957,7 @@
         <v>11</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>248</v>
+        <v>325</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2" t="s">
